--- a/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
@@ -69,21 +69,21 @@
     <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
     <t xml:space="preserve">Carahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Saavedra</t>
+    <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
@@ -96,24 +96,24 @@
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
+    <t xml:space="preserve">Collipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
+    <t xml:space="preserve">Villarrica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
-    <t xml:space="preserve">Villarrica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vilcún</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,7 +574,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>145.28</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>138.34</v>
+        <v>149.35</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>134.99</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>132.07</v>
+        <v>141.73</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>128.86</v>
+        <v>141.04</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +659,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>128.36</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.51</v>
+        <v>137.29</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>125.26</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>121.49</v>
+        <v>131.58</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>121.06</v>
+        <v>128.81</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>119.65</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="13">
@@ -755,13 +755,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9211</v>
+        <v>9116</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>117.82</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="14">
@@ -772,13 +772,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9102</v>
+        <v>9211</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>117.39</v>
+        <v>126.87</v>
       </c>
     </row>
     <row r="15">
@@ -789,13 +789,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9116</v>
+        <v>9102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>116.82</v>
+        <v>126.54</v>
       </c>
     </row>
     <row r="16">
@@ -806,13 +806,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9208</v>
+        <v>9207</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>114.76</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="17">
@@ -823,13 +823,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>113.4</v>
+        <v>123.95</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>113.14</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>107.87</v>
+        <v>116.38</v>
       </c>
     </row>
     <row r="20">
@@ -880,7 +880,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>105.81</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>104.51</v>
+        <v>113.08</v>
       </c>
     </row>
     <row r="22">
@@ -908,13 +908,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9209</v>
+        <v>9202</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>100.17</v>
+        <v>107.88</v>
       </c>
     </row>
     <row r="23">
@@ -925,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9101</v>
+        <v>9209</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>99.96</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9202</v>
+        <v>9101</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>99.84</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="25">
@@ -965,7 +965,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>94.66</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="26">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9205</v>
+        <v>9120</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>94.39</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="27">
@@ -993,13 +993,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>9120</v>
+        <v>9205</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>94.13</v>
+        <v>99.92</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>91.86</v>
+        <v>98.43</v>
       </c>
     </row>
     <row r="29">
@@ -1033,7 +1033,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>90.36</v>
+        <v>96.71</v>
       </c>
     </row>
     <row r="30">
@@ -1050,7 +1050,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>88.21</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>86.42</v>
+        <v>92.71</v>
       </c>
     </row>
     <row r="32">
@@ -1084,7 +1084,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.22</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="33">
@@ -1101,7 +1101,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>76.61</v>
+        <v>81.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:04</t>
+    <t xml:space="preserve">2026-10-05 16:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
